--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484553_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484553_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.723699999999999</v>
+        <v>8.407500000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>4.234</v>
+        <v>4.0417</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4897</v>
+        <v>4.3658</v>
       </c>
       <c r="G2" t="n">
         <v>6.3867</v>
@@ -610,13 +610,13 @@
         <v>1.6493</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7688</v>
+        <v>1.4527</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6946</v>
+        <v>0.5023</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0743</v>
+        <v>0.9504</v>
       </c>
       <c r="V2" t="n">
         <v>0.9346</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0272</v>
+        <v>4.937</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4568</v>
+        <v>1.1684</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5704</v>
+        <v>3.7686</v>
       </c>
       <c r="G3" t="n">
         <v>2.6731</v>
@@ -688,13 +688,13 @@
         <v>1.6493</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1397</v>
+        <v>1.0494</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4744</v>
+        <v>0.1859</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6653</v>
+        <v>0.8635</v>
       </c>
       <c r="V3" t="n">
         <v>0.6647</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. YURCHENKO</t>
+          <t>J. GOMEZ CARBONELL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4159</v>
+        <v>3.3643</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7623</v>
+        <v>3.6966</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6536</v>
+        <v>-0.3323</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7772</v>
+        <v>0.3881</v>
       </c>
       <c r="H4" t="n">
-        <v>1.181</v>
+        <v>0.5128</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5962</v>
+        <v>-0.1247</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1303</v>
+        <v>1.1042</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8545</v>
+        <v>0.8762</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2758</v>
+        <v>0.2281</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6469</v>
+        <v>-0.7161</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3265</v>
+        <v>-0.3633</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3204</v>
+        <v>-0.3528</v>
       </c>
       <c r="P4" t="n">
+        <v>1.2828</v>
+      </c>
+      <c r="Q4" t="n">
         <v>-0.1833</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-1.0995</v>
-      </c>
       <c r="R4" t="n">
-        <v>0.9163</v>
+        <v>1.4661</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8427</v>
+        <v>0.4265</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7315</v>
+        <v>0.2417</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1112</v>
+        <v>0.1847</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.0208</v>
+        <v>1.267</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.5339</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.0208</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. GOMEZ CARBONELL</t>
+          <t>P. VILLAGRASA TORTAJADA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.3122</v>
+        <v>3.265</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5454</v>
+        <v>3.5689</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2332</v>
+        <v>-0.3039</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3881</v>
+        <v>4.746</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5128</v>
+        <v>3.0921</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1247</v>
+        <v>1.6539</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1042</v>
+        <v>5.6225</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8762</v>
+        <v>3.4554</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2281</v>
+        <v>2.1671</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7161</v>
+        <v>-0.8764999999999999</v>
       </c>
       <c r="N5" t="n">
         <v>-0.3633</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3528</v>
+        <v>-0.5131</v>
       </c>
       <c r="P5" t="n">
+        <v>-0.5498</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-1.8326</v>
+      </c>
+      <c r="R5" t="n">
         <v>1.2828</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-0.1833</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.4661</v>
-      </c>
       <c r="S5" t="n">
-        <v>0.3744</v>
+        <v>-0.2977</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0905</v>
+        <v>-0.221</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2838</v>
+        <v>-0.0767</v>
       </c>
       <c r="V5" t="n">
-        <v>1.267</v>
+        <v>-0.6335</v>
       </c>
       <c r="W5" t="n">
-        <v>2.5339</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.267</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.633</v>
+        <v>2.9984</v>
       </c>
       <c r="E6" t="n">
-        <v>1.633</v>
+        <v>2.0727</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0.9257</v>
       </c>
       <c r="G6" t="n">
         <v>1.6735</v>
@@ -922,13 +922,13 @@
         <v>1.6493</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6898</v>
+        <v>-0.3245</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6606</v>
+        <v>-0.221</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0292</v>
+        <v>-0.1035</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. DE LA CAL DOMINGUEZ</t>
+          <t>S. YURCHENKO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5992</v>
+        <v>2.6597</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4332</v>
+        <v>0.3777</v>
       </c>
       <c r="F7" t="n">
-        <v>1.166</v>
+        <v>2.282</v>
       </c>
       <c r="G7" t="n">
-        <v>2.8577</v>
+        <v>1.7772</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0657</v>
+        <v>1.181</v>
       </c>
       <c r="I7" t="n">
-        <v>1.792</v>
+        <v>0.5962</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9007</v>
+        <v>1.1303</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5573</v>
+        <v>0.8545</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3434</v>
+        <v>0.2758</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.043</v>
+        <v>0.6469</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4916</v>
+        <v>0.3265</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4486</v>
+        <v>0.3204</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9163</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1991</v>
+        <v>-1.0995</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2828</v>
+        <v>0.9163</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3016</v>
+        <v>1.0865</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7315</v>
+        <v>0.3469</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.7396</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6439</v>
+        <v>-0.0208</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6439</v>
+        <v>-0.0208</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. VILLAGRASA TORTAJADA</t>
+          <t>A. MONRABAL ROMEU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.5529</v>
+        <v>2.2274</v>
       </c>
       <c r="E8" t="n">
-        <v>3.1293</v>
+        <v>-1.6179</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5764</v>
+        <v>3.8453</v>
       </c>
       <c r="G8" t="n">
-        <v>4.746</v>
+        <v>1.8295</v>
       </c>
       <c r="H8" t="n">
-        <v>3.0921</v>
+        <v>0.9897</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6539</v>
+        <v>0.8399</v>
       </c>
       <c r="J8" t="n">
-        <v>5.6225</v>
+        <v>0.4134</v>
       </c>
       <c r="K8" t="n">
-        <v>3.4554</v>
+        <v>0.2785</v>
       </c>
       <c r="L8" t="n">
-        <v>2.1671</v>
+        <v>0.1349</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8764999999999999</v>
+        <v>1.4161</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3633</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5131</v>
+        <v>0.705</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5498</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8326</v>
+        <v>-2.1991</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2828</v>
+        <v>1.8326</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0099</v>
+        <v>1.0863</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6606</v>
+        <v>0.1678</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3493</v>
+        <v>0.9185</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6335</v>
+        <v>-0.3219</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6335</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.0274</v>
+        <v>1.9703</v>
       </c>
       <c r="E9" t="n">
-        <v>0.849</v>
+        <v>0.5194</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1784</v>
+        <v>1.4509</v>
       </c>
       <c r="G9" t="n">
         <v>0.3991</v>
@@ -1156,13 +1156,13 @@
         <v>1.4661</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6387</v>
+        <v>0.5816</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6395</v>
+        <v>0.31</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0008</v>
+        <v>0.2717</v>
       </c>
       <c r="V9" t="n">
         <v>0.6231</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. HATHOUTI LAHRECH</t>
+          <t>A. DE LA CAL DOMINGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1884</v>
+        <v>1.8707</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0568</v>
+        <v>0.9524</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2452</v>
+        <v>0.9183</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5891</v>
+        <v>2.8577</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6212</v>
+        <v>1.0657</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0321</v>
+        <v>1.792</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1084</v>
+        <v>2.9007</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1084</v>
+        <v>1.5573</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.3434</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4807</v>
+        <v>-0.043</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5128</v>
+        <v>-0.4916</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0321</v>
+        <v>0.4486</v>
       </c>
       <c r="P10" t="n">
-        <v>0.733</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.1991</v>
       </c>
       <c r="R10" t="n">
-        <v>0.733</v>
+        <v>1.2828</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1337</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1652</v>
+        <v>0.2508</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0314</v>
+        <v>0.3224</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. MONRABAL ROMEU</t>
+          <t>S. HATHOUTI LAHRECH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1638</v>
+        <v>1.3589</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4833</v>
+        <v>0.0394</v>
       </c>
       <c r="F11" t="n">
-        <v>3.6471</v>
+        <v>1.3195</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8295</v>
+        <v>0.5891</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9897</v>
+        <v>0.6212</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8399</v>
+        <v>-0.0321</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4134</v>
+        <v>0.1084</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2785</v>
+        <v>0.1084</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1349</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.4161</v>
+        <v>0.4807</v>
       </c>
       <c r="N11" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.5128</v>
       </c>
       <c r="O11" t="n">
-        <v>0.705</v>
+        <v>-0.0321</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3665</v>
+        <v>0.733</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.1991</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8326</v>
+        <v>0.733</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0228</v>
+        <v>0.0368</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6976</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7203000000000001</v>
+        <v>0.1058</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2558</v>
+        <v>0.1156</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4216</v>
+        <v>-3.4627</v>
       </c>
       <c r="F12" t="n">
-        <v>3.6774</v>
+        <v>3.5783</v>
       </c>
       <c r="G12" t="n">
         <v>0.0571</v>
@@ -1390,13 +1390,13 @@
         <v>1.6493</v>
       </c>
       <c r="S12" t="n">
-        <v>1.8035</v>
+        <v>1.6633</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3643</v>
+        <v>0.3232</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4392</v>
+        <v>1.3401</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3219</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>32.8995</v>
+        <v>33.1748</v>
       </c>
       <c r="E13" t="n">
-        <v>11.0813</v>
+        <v>11.3566</v>
       </c>
       <c r="F13" t="n">
         <v>21.8182</v>
@@ -1447,7 +1447,7 @@
         <v>11.2195</v>
       </c>
       <c r="L13" t="n">
-        <v>9.4594</v>
+        <v>9.459399999999999</v>
       </c>
       <c r="M13" t="n">
         <v>2.6983</v>
@@ -1459,7 +1459,7 @@
         <v>0.9592999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9162000000000003</v>
+        <v>0.9161999999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-14.6605</v>
@@ -1468,13 +1468,13 @@
         <v>15.5769</v>
       </c>
       <c r="S13" t="n">
-        <v>7.058800000000002</v>
+        <v>7.334000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5423</v>
+        <v>1.8176</v>
       </c>
       <c r="U13" t="n">
-        <v>5.516299999999999</v>
+        <v>5.516500000000001</v>
       </c>
       <c r="V13" t="n">
         <v>1.5474</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. DIAGNE</t>
+          <t>C. CAMAHORT TORRES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8982</v>
+        <v>-0.4083</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4569</v>
+        <v>-0.4419</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5587</v>
+        <v>0.0336</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.0871</v>
+        <v>-0.5489000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.3111</v>
+        <v>-0.8148</v>
       </c>
       <c r="I15" t="n">
-        <v>0.224</v>
+        <v>0.266</v>
       </c>
       <c r="J15" t="n">
-        <v>2.6624</v>
+        <v>0.0633</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5787</v>
+        <v>0.0217</v>
       </c>
       <c r="L15" t="n">
-        <v>2.0837</v>
+        <v>0.0417</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.7495</v>
+        <v>-0.6122</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.8898</v>
+        <v>-0.8365</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.8597</v>
+        <v>0.2243</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.0158</v>
+        <v>1.2828</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.6651</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6493</v>
+        <v>1.2828</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4464</v>
+        <v>-0.8203</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5279</v>
+        <v>-0.5053</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9184</v>
+        <v>-0.3151</v>
       </c>
       <c r="V15" t="n">
-        <v>2.5548</v>
+        <v>-0.3219</v>
       </c>
       <c r="W15" t="n">
-        <v>1.9317</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6231</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. CAMAHORT TORRES</t>
+          <t>E. DIAGNE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5059</v>
+        <v>-0.7497</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6342</v>
+        <v>0.3992</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1283</v>
+        <v>-1.1489</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5489000000000001</v>
+        <v>-1.0871</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8148</v>
+        <v>-1.3111</v>
       </c>
       <c r="I16" t="n">
-        <v>0.266</v>
+        <v>0.224</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0633</v>
+        <v>2.6624</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0217</v>
+        <v>0.5787</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0417</v>
+        <v>2.0837</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6122</v>
+        <v>-3.7495</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8365</v>
+        <v>-1.8898</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2243</v>
+        <v>-1.8597</v>
       </c>
       <c r="P16" t="n">
-        <v>1.2828</v>
+        <v>-2.0158</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-3.6651</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2828</v>
+        <v>1.6493</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9179</v>
+        <v>-0.2015</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6976</v>
+        <v>-0.5298</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2203</v>
+        <v>0.3282</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3219</v>
+        <v>2.5548</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.9317</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3219</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. ABAD MOLINER</t>
+          <t>R. HOLGADO CUELLAR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.5916</v>
+        <v>-1.4064</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6808</v>
+        <v>-0.2431</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0892</v>
+        <v>-1.1633</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4315</v>
+        <v>0.2844</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1679</v>
+        <v>-1.0205</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5994</v>
+        <v>1.3049</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5994</v>
+        <v>2.356</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>-0.2634</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5994</v>
+        <v>2.6194</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1679</v>
+        <v>-2.0716</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1679</v>
+        <v>-0.7572</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-1.3145</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9163</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.6493</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2438</v>
+        <v>-1.5075</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1652</v>
+        <v>-0.7665999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.741</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. HOLGADO CUELLAR</t>
+          <t>M. ABAD MOLINER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6803</v>
+        <v>-1.5173</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3392</v>
+        <v>-1.6808</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.341</v>
+        <v>0.1635</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2844</v>
+        <v>-0.4315</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0205</v>
+        <v>0.1679</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3049</v>
+        <v>-0.5994</v>
       </c>
       <c r="J18" t="n">
-        <v>2.356</v>
+        <v>-0.5994</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2634</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>2.6194</v>
+        <v>-0.5994</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.0716</v>
+        <v>0.1679</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7572</v>
+        <v>0.1679</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.3145</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1833</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6493</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.7814</v>
+        <v>-0.1695</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8627</v>
+        <v>-0.1652</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9187</v>
+        <v>-0.0043</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2909</v>
+        <v>-1.7839</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4664</v>
+        <v>-1.8895</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1755</v>
+        <v>0.1055</v>
       </c>
       <c r="G19" t="n">
         <v>-1.345</v>
@@ -1936,13 +1936,13 @@
         <v>2.3823</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2128</v>
+        <v>-0.7059</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.377</v>
+        <v>-0.8001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1642</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="V19" t="n">
         <v>0.6335</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5994</v>
+        <v>-2.5688</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8442</v>
+        <v>-1.0366</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7552</v>
+        <v>-1.5322</v>
       </c>
       <c r="G20" t="n">
         <v>-3.6161</v>
@@ -2014,13 +2014,13 @@
         <v>1.4661</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1274</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1666</v>
+        <v>-0.359</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0393</v>
+        <v>0.2622</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3219</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. ALBA GONZALEZ</t>
+          <t>D. KEITH CAMARA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8297</v>
+        <v>-3.7396</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2467</v>
+        <v>-2.8791</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.583</v>
+        <v>-0.8605</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6578</v>
+        <v>-2.5433</v>
       </c>
       <c r="H21" t="n">
-        <v>0.878</v>
+        <v>-2.2901</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.5358</v>
+        <v>-0.2532</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3492</v>
+        <v>-0.4228</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8079</v>
+        <v>-1.0995</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.157</v>
+        <v>0.6766</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3086</v>
+        <v>-2.1205</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0701</v>
+        <v>-1.1907</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3787</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3665</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4661</v>
+        <v>1.2828</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8604000000000001</v>
+        <v>-0.6465</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4419</v>
+        <v>-0.9457</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4185</v>
+        <v>0.2992</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.945</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.6231</v>
+        <v>0.3219</v>
       </c>
       <c r="X21" t="n">
         <v>-0.3219</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. KEITH CAMARA</t>
+          <t>A. ALBA GONZALEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.254</v>
+        <v>-3.799</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0714</v>
+        <v>-3.439</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1825</v>
+        <v>-0.36</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.5433</v>
+        <v>-1.6578</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.2901</v>
+        <v>0.878</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2532</v>
+        <v>-2.5358</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4228</v>
+        <v>-0.3492</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.0995</v>
+        <v>0.8079</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6766</v>
+        <v>-1.157</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1205</v>
+        <v>-1.3086</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1907</v>
+        <v>0.0701</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-1.3787</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5498</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2828</v>
+        <v>1.4661</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1608</v>
+        <v>-0.8297</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.138</v>
+        <v>-0.6342</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0229</v>
+        <v>-0.1955</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.945</v>
       </c>
       <c r="W22" t="n">
-        <v>0.3219</v>
+        <v>-0.6231</v>
       </c>
       <c r="X22" t="n">
         <v>-0.3219</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.857100000000001</v>
+        <v>-8.3165</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.2832</v>
+        <v>-6.9947</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5739</v>
+        <v>-1.3218</v>
       </c>
       <c r="G23" t="n">
         <v>-6.4281</v>
@@ -2248,13 +2248,13 @@
         <v>2.0158</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6776</v>
+        <v>-1.1371</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8816000000000001</v>
+        <v>-0.5931</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.796</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9346</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.4642</v>
+        <v>-9.244199999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.9842</v>
+        <v>-4.888</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.48</v>
+        <v>-4.3562</v>
       </c>
       <c r="G24" t="n">
         <v>-7.279</v>
@@ -2326,13 +2326,13 @@
         <v>1.4661</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.523</v>
+        <v>-0.303</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3137</v>
+        <v>-0.2175</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2093</v>
+        <v>-0.0854</v>
       </c>
       <c r="V24" t="n">
         <v>-2.212</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-32.8996</v>
+        <v>-32.2584</v>
       </c>
       <c r="E25" t="n">
-        <v>-21.8181</v>
+        <v>-21.8182</v>
       </c>
       <c r="F25" t="n">
-        <v>-11.0813</v>
+        <v>-10.4403</v>
       </c>
       <c r="G25" t="n">
         <v>-23.3771</v>
@@ -2377,13 +2377,13 @@
         <v>-10.4186</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.698599999999999</v>
+        <v>-2.6986</v>
       </c>
       <c r="K25" t="n">
         <v>-1.739</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.9593000000000007</v>
+        <v>-0.9592999999999998</v>
       </c>
       <c r="M25" t="n">
         <v>-20.6787</v>
@@ -2395,7 +2395,7 @@
         <v>-9.459300000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.9162000000000002</v>
+        <v>-0.9162</v>
       </c>
       <c r="Q25" t="n">
         <v>-15.577</v>
@@ -2404,13 +2404,13 @@
         <v>14.6606</v>
       </c>
       <c r="S25" t="n">
-        <v>-7.0587</v>
+        <v>-6.4177</v>
       </c>
       <c r="T25" t="n">
-        <v>-5.5164</v>
+        <v>-5.5165</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.5425</v>
+        <v>-0.9014000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>-1.5471</v>
